--- a/medical_application_forms/019_infection_control_discharge_form--medical_application_forms.xlsx
+++ b/medical_application_forms/019_infection_control_discharge_form--medical_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -914,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -998,46 +998,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>antimicrobial</t>
+          <t>antiviral</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Antimicrobial</t>
+          <t>Antiviral</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>infection_control_measures_choices</t>
+          <t>antibiotic_allergy_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>antiviral</t>
+          <t>penicillin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Antiviral</t>
+          <t>Penicillin</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>infection_control_measures_choices</t>
+          <t>antibiotic_allergy_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>antiviral</t>
+          <t>cephalosporin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Antiviral</t>
+          <t>Cephalosporin</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>penicillin</t>
+          <t>vancomycin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Penicillin</t>
+          <t>Vancomycin</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>cephalosporin</t>
+          <t>ciprofloxacin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cephalosporin</t>
+          <t>Ciprofloxacin</t>
         </is>
       </c>
     </row>
@@ -1083,46 +1083,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>vancomycin</t>
+          <t>azilsam</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vancomycin</t>
+          <t>Azilsam</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>antibiotic_allergy_choices</t>
+          <t>medication_allergies_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ciprofloxacin</t>
+          <t>aspirin</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ciprofloxacin</t>
+          <t>Aspirin</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>antibiotic_allergy_choices</t>
+          <t>medication_allergies_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>azilsam</t>
+          <t>penicillin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azilsam</t>
+          <t>Penicillin</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>aspirin</t>
+          <t>sulfa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aspirin</t>
+          <t>Sulfa</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>penicillin</t>
+          <t>amphotrcin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Penicillin</t>
+          <t>Amphotrcin</t>
         </is>
       </c>
     </row>
@@ -1168,46 +1168,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sulfa</t>
+          <t>cephalosporin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sulfa</t>
+          <t>Cephalosporin</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>medication_allergies_choices</t>
+          <t>infection_control_status_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>amphotrcin</t>
+          <t>not_at_risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amphotrcin</t>
+          <t>Not at risk</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>medication_allergies_choices</t>
+          <t>infection_control_status_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>cephalosporin</t>
+          <t>at_risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cephalosporin</t>
+          <t>At risk</t>
         </is>
       </c>
     </row>
@@ -1219,53 +1219,53 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_at_risk</t>
+          <t>high_risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Not at risk</t>
+          <t>High risk</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>infection_control_status_choices</t>
+          <t>physician_comments_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>at_risk</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>At risk</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>infection_control_status_choices</t>
+          <t>physician_comments_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>high_risk</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>High risk</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>physician_comments_choices</t>
+          <t>patient_comments_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>physician_comments_choices</t>
+          <t>patient_comments_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1291,40 +1291,6 @@
         </is>
       </c>
       <c r="C22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>patient_comments_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>patient_comments_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
         <is>
           <t>No</t>
         </is>
